--- a/poker/resources/sample/Blackjack.xlsx
+++ b/poker/resources/sample/Blackjack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Blackjack" sheetId="34" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -1213,10 +1213,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="2"/>
+    <col min="1" max="1" width="10.375" style="2"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
@@ -1520,6 +1520,156 @@
         <v>33</v>
       </c>
     </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2">
+        <v>30010021</v>
+      </c>
+      <c r="B8" s="1">
+        <v>300100</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="2">
+        <v>100001</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6</v>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>200</v>
+      </c>
+      <c r="K8" s="2">
+        <v>150</v>
+      </c>
+      <c r="L8" s="2">
+        <v>150</v>
+      </c>
+      <c r="M8" s="2">
+        <v>100</v>
+      </c>
+      <c r="N8" s="2">
+        <v>100</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="2">
+        <v>30010022</v>
+      </c>
+      <c r="B9" s="1">
+        <v>300100</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1">
+        <v>22</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="2">
+        <v>100001</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>200</v>
+      </c>
+      <c r="K9" s="2">
+        <v>150</v>
+      </c>
+      <c r="L9" s="2">
+        <v>150</v>
+      </c>
+      <c r="M9" s="2">
+        <v>100</v>
+      </c>
+      <c r="N9" s="2">
+        <v>100</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2">
+        <v>30010023</v>
+      </c>
+      <c r="B10" s="1">
+        <v>300100</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
+        <v>23</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="2">
+        <v>100001</v>
+      </c>
+      <c r="G10" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>200</v>
+      </c>
+      <c r="K10" s="2">
+        <v>150</v>
+      </c>
+      <c r="L10" s="2">
+        <v>150</v>
+      </c>
+      <c r="M10" s="2">
+        <v>100</v>
+      </c>
+      <c r="N10" s="2">
+        <v>100</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/Blackjack.xlsx
+++ b/poker/resources/sample/Blackjack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Blackjack" sheetId="34" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -1213,10 +1213,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="2"/>
+    <col min="1" max="1" width="9.25" style="2"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
@@ -1520,156 +1520,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2">
-        <v>30010021</v>
-      </c>
-      <c r="B8" s="1">
-        <v>300100</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2">
-        <v>100001</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H8" s="2">
-        <v>6</v>
-      </c>
-      <c r="I8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>200</v>
-      </c>
-      <c r="K8" s="2">
-        <v>150</v>
-      </c>
-      <c r="L8" s="2">
-        <v>150</v>
-      </c>
-      <c r="M8" s="2">
-        <v>100</v>
-      </c>
-      <c r="N8" s="2">
-        <v>100</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="2">
-        <v>30010022</v>
-      </c>
-      <c r="B9" s="1">
-        <v>300100</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1">
-        <v>22</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2">
-        <v>100001</v>
-      </c>
-      <c r="G9" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="H9" s="2">
-        <v>6</v>
-      </c>
-      <c r="I9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>200</v>
-      </c>
-      <c r="K9" s="2">
-        <v>150</v>
-      </c>
-      <c r="L9" s="2">
-        <v>150</v>
-      </c>
-      <c r="M9" s="2">
-        <v>100</v>
-      </c>
-      <c r="N9" s="2">
-        <v>100</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="2">
-        <v>30010023</v>
-      </c>
-      <c r="B10" s="1">
-        <v>300100</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1">
-        <v>23</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="2">
-        <v>100001</v>
-      </c>
-      <c r="G10" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="H10" s="2">
-        <v>6</v>
-      </c>
-      <c r="I10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>200</v>
-      </c>
-      <c r="K10" s="2">
-        <v>150</v>
-      </c>
-      <c r="L10" s="2">
-        <v>150</v>
-      </c>
-      <c r="M10" s="2">
-        <v>100</v>
-      </c>
-      <c r="N10" s="2">
-        <v>100</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
